--- a/excel/exchange.xlsx
+++ b/excel/exchange.xlsx
@@ -85,7 +85,8 @@
   </si>
   <si>
     <t>兑换条件
-格式: 条件id_参数</t>
+格式:
+条件id_参数值_可选参数数组</t>
   </si>
   <si>
     <t>兑换价格</t>
@@ -1363,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" spans="1:7">
+    <row r="3" ht="54" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
